--- a/portfolio_allocations/XMME_allocation.xlsx
+++ b/portfolio_allocations/XMME_allocation.xlsx
@@ -6,7 +6,7 @@
     <x:workbookView/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet name="2026-04-12" sheetId="2" r:id="R56321f94b9544144"/>
+    <x:sheet name="2026-04-12" sheetId="2" r:id="Rfb32736aee5c4146"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/portfolio_allocations/XMME_allocation.xlsx
+++ b/portfolio_allocations/XMME_allocation.xlsx
@@ -6,7 +6,7 @@
     <x:workbookView/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet name="2026-04-21" sheetId="2" r:id="R0a21b7e8f46e4a9c"/>
+    <x:sheet name="2026-04-21" sheetId="2" r:id="Rfea94b578a4e4fe7"/>
   </x:sheets>
 </x:workbook>
 </file>
